--- a/Seat.xlsx
+++ b/Seat.xlsx
@@ -15,11 +15,12 @@
     <sheet name="Seat" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="163">
   <si>
     <t>Seat1</t>
   </si>
@@ -343,6 +344,171 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>s/n</t>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>okegbile Yusroh</t>
+  </si>
+  <si>
+    <t>Okegbile Monsuroh</t>
+  </si>
+  <si>
+    <t>Akinwale Nasiroh</t>
+  </si>
+  <si>
+    <t>Akinlabi Aisha</t>
+  </si>
+  <si>
+    <t>Abdulafeez Rahmatallahi</t>
+  </si>
+  <si>
+    <t>Mojeed Misturah</t>
+  </si>
+  <si>
+    <t>Ajibola Khadijah</t>
+  </si>
+  <si>
+    <t>Qoseem Nihotallahi</t>
+  </si>
+  <si>
+    <t>Muhammed Habeebah</t>
+  </si>
+  <si>
+    <t>Tajudeen Sofiyyah</t>
+  </si>
+  <si>
+    <t>Olalekan Mutmainah</t>
+  </si>
+  <si>
+    <t>Kazeem Aishah</t>
+  </si>
+  <si>
+    <t>Adewale Firdaus</t>
+  </si>
+  <si>
+    <t>Arowolo Muslimah</t>
+  </si>
+  <si>
+    <t>Alabi Ameenah</t>
+  </si>
+  <si>
+    <t>Adeaa Hassanah</t>
+  </si>
+  <si>
+    <t>Adeaga Aisha</t>
+  </si>
+  <si>
+    <t>Qomorudeen Raheemah</t>
+  </si>
+  <si>
+    <t>Olatoye Azeezah</t>
+  </si>
+  <si>
+    <t>Jimoh Muhsinat</t>
+  </si>
+  <si>
+    <t>A'rosheed Aliyah</t>
+  </si>
+  <si>
+    <t>Basheer Khadijah</t>
+  </si>
+  <si>
+    <t>Abass Fathia</t>
+  </si>
+  <si>
+    <t>Abdullah Monsuroh</t>
+  </si>
+  <si>
+    <t>Hassan Islamiyyah</t>
+  </si>
+  <si>
+    <t>Muhammad A'Ganiyy</t>
+  </si>
+  <si>
+    <t>Alameen Faoziyyah</t>
+  </si>
+  <si>
+    <t>Akinlabi Ameerah</t>
+  </si>
+  <si>
+    <t>Akeeb Muideen</t>
+  </si>
+  <si>
+    <t>Abdulateef Abdulsalam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Badmus Awwal </t>
+  </si>
+  <si>
+    <t>Mustapha Muktar</t>
+  </si>
+  <si>
+    <t>Yusuff Abdulsalam</t>
+  </si>
+  <si>
+    <t>Ibraheem Awwal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdulateef Muktar </t>
+  </si>
+  <si>
+    <t>Amzal Muhammad Awwal</t>
+  </si>
+  <si>
+    <t>Kilani Tijani</t>
+  </si>
+  <si>
+    <t>Durodola Abdul-Basit</t>
+  </si>
+  <si>
+    <t>Hammed Idris</t>
+  </si>
+  <si>
+    <t>Oyewole Abdulsalam</t>
+  </si>
+  <si>
+    <t>Abdullahi Awwal</t>
+  </si>
+  <si>
+    <t>Abdulhammed Abdulmalik</t>
+  </si>
+  <si>
+    <t>Hassan Hammed</t>
+  </si>
+  <si>
+    <t>Abdulsalam Jamal</t>
+  </si>
+  <si>
+    <t>Abdulateef Abdulrafiu</t>
+  </si>
+  <si>
+    <t>Aliyu Adam</t>
+  </si>
+  <si>
+    <t>Musliu Abdulsalam</t>
+  </si>
+  <si>
+    <t>Test 1</t>
+  </si>
+  <si>
+    <t>Test 2</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Exam</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -886,17 +1052,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -954,6 +1120,64 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A62:H109" totalsRowShown="0">
+  <autoFilter ref="A62:H109"/>
+  <sortState ref="A63:H109">
+    <sortCondition descending="1" ref="G62:G109"/>
+  </sortState>
+  <tableColumns count="8">
+    <tableColumn id="1" name="s/n"/>
+    <tableColumn id="2" name="Names"/>
+    <tableColumn id="3" name="Test 1"/>
+    <tableColumn id="4" name="Test 2"/>
+    <tableColumn id="5" name="Test">
+      <calculatedColumnFormula>C63+D63</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Exam"/>
+    <tableColumn id="7" name="Total">
+      <calculatedColumnFormula>E63+F63</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="Position"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="J62:Q88" totalsRowShown="0">
+  <autoFilter ref="J62:Q88"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="s/n"/>
+    <tableColumn id="2" name="Names"/>
+    <tableColumn id="3" name="Test 1"/>
+    <tableColumn id="4" name="Test 2"/>
+    <tableColumn id="5" name="Test"/>
+    <tableColumn id="6" name="Exam"/>
+    <tableColumn id="7" name="Total"/>
+    <tableColumn id="8" name="Position"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="J91:Q112" totalsRowShown="0">
+  <autoFilter ref="J91:Q112"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="s/n"/>
+    <tableColumn id="2" name="Names"/>
+    <tableColumn id="3" name="Test 1"/>
+    <tableColumn id="4" name="Test 2"/>
+    <tableColumn id="5" name="Test"/>
+    <tableColumn id="6" name="Exam"/>
+    <tableColumn id="7" name="Total"/>
+    <tableColumn id="8" name="Column1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1219,14 +1443,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:Q112"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1237,12 +1467,12 @@
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
       <c r="E2" s="2"/>
       <c r="F2" s="1"/>
     </row>
@@ -1512,10 +1742,10 @@
       <c r="I10" s="5">
         <v>9</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="11"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
@@ -1538,10 +1768,10 @@
       <c r="I11" s="5">
         <v>10</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="K11" s="11"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
@@ -1562,10 +1792,10 @@
       <c r="I12" s="5">
         <v>11</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="K12" s="11"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
@@ -1584,16 +1814,16 @@
       <c r="I13" s="5">
         <v>12</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="2"/>
       <c r="F14">
         <v>5</v>
@@ -1604,20 +1834,20 @@
       <c r="I14" s="5">
         <v>13</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="K14" s="11"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="8">
         <v>6</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="2"/>
       <c r="F15">
         <v>6</v>
@@ -1628,14 +1858,14 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="8">
         <v>7</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="2"/>
       <c r="F16">
         <v>7</v>
@@ -1646,14 +1876,14 @@
       <c r="H16" s="5"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="8">
         <v>8</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="2"/>
       <c r="F17">
         <v>8</v>
@@ -1840,43 +2070,43 @@
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
       <c r="E34" s="2"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="8">
         <v>5</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
       <c r="E35" s="2"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="8">
         <v>6</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
       <c r="E36" s="2"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="8">
         <v>5</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
       <c r="E37" s="2"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1886,8 +2116,8 @@
       <c r="B38" s="2">
         <v>1</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
       <c r="E38" s="2"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1898,8 +2128,8 @@
         <f>SUM(B35:B38)</f>
         <v>17</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
       <c r="E39" s="2"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -1910,12 +2140,12 @@
       <c r="E40" s="2"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
       <c r="E41" s="2"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2017,7 +2247,7 @@
       </c>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
         <v>21</v>
       </c>
@@ -2032,7 +2262,7 @@
       </c>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="9"/>
       <c r="B50" s="3" t="s">
         <v>70</v>
@@ -2045,7 +2275,7 @@
       </c>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
         <v>28</v>
       </c>
@@ -2054,65 +2284,65 @@
       <c r="D51" s="3"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="9"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="2"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="10"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B54" s="4">
         <v>7</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B55" s="4">
         <v>7</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>105</v>
       </c>
       <c r="B56" s="4">
         <v>7</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>106</v>
       </c>
       <c r="B57" s="4">
         <v>3</v>
       </c>
-      <c r="C57" s="10"/>
-      <c r="D57" s="10"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>107</v>
       </c>
@@ -2120,25 +2350,1361 @@
         <f>SUM(B54:B57)</f>
         <v>24</v>
       </c>
-      <c r="C58" s="10"/>
-      <c r="D58" s="10"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="I61" t="s">
         <v>45</v>
       </c>
     </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" t="s">
+        <v>157</v>
+      </c>
+      <c r="D62" t="s">
+        <v>158</v>
+      </c>
+      <c r="E62" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" t="s">
+        <v>160</v>
+      </c>
+      <c r="G62" t="s">
+        <v>107</v>
+      </c>
+      <c r="H62" t="s">
+        <v>161</v>
+      </c>
+      <c r="J62" t="s">
+        <v>108</v>
+      </c>
+      <c r="K62" t="s">
+        <v>109</v>
+      </c>
+      <c r="L62" t="s">
+        <v>157</v>
+      </c>
+      <c r="M62" t="s">
+        <v>158</v>
+      </c>
+      <c r="N62" t="s">
+        <v>159</v>
+      </c>
+      <c r="O62" t="s">
+        <v>160</v>
+      </c>
+      <c r="P62" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2</v>
+      </c>
+      <c r="B63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C63">
+        <v>10</v>
+      </c>
+      <c r="D63">
+        <v>20</v>
+      </c>
+      <c r="E63">
+        <f t="shared" ref="E63:E109" si="0">C63+D63</f>
+        <v>30</v>
+      </c>
+      <c r="F63">
+        <v>62</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ref="G63:G109" si="1">E63+F63</f>
+        <v>92</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>113</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
+      </c>
+      <c r="D64">
+        <v>20</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="F64">
+        <v>44</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65">
+        <v>10</v>
+      </c>
+      <c r="D65">
+        <v>15</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="F65">
+        <v>42</v>
+      </c>
+      <c r="G65">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>110</v>
+      </c>
+      <c r="C66">
+        <v>10</v>
+      </c>
+      <c r="D66">
+        <v>16</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="F66">
+        <v>39</v>
+      </c>
+      <c r="G66">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+      <c r="K66" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67">
+        <v>4</v>
+      </c>
+      <c r="D67">
+        <v>15</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F67">
+        <v>45</v>
+      </c>
+      <c r="G67">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
+      <c r="K67" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>28</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
+      </c>
+      <c r="D68">
+        <v>14</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="F68">
+        <v>32</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="J68">
+        <v>6</v>
+      </c>
+      <c r="K68" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>115</v>
+      </c>
+      <c r="C69">
+        <v>6</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="F69">
+        <v>36</v>
+      </c>
+      <c r="G69">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="J69">
+        <v>7</v>
+      </c>
+      <c r="K69" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>17</v>
+      </c>
+      <c r="B70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="D70">
+        <v>2</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F70">
+        <v>40</v>
+      </c>
+      <c r="G70">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="J70">
+        <v>8</v>
+      </c>
+      <c r="K70" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>26</v>
+      </c>
+      <c r="B71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71">
+        <v>4</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F71">
+        <v>35</v>
+      </c>
+      <c r="G71">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="J71">
+        <v>9</v>
+      </c>
+      <c r="K71" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>19</v>
+      </c>
+      <c r="B72" t="s">
+        <v>127</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72">
+        <v>3</v>
+      </c>
+      <c r="E72">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F72">
+        <v>31</v>
+      </c>
+      <c r="G72">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="J72">
+        <v>10</v>
+      </c>
+      <c r="K72" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>16</v>
+      </c>
+      <c r="B73" t="s">
+        <v>124</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F73">
+        <v>31</v>
+      </c>
+      <c r="G73">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="J73">
+        <v>11</v>
+      </c>
+      <c r="K73" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+      <c r="D74">
+        <v>4</v>
+      </c>
+      <c r="E74">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <v>24</v>
+      </c>
+      <c r="G74">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J74">
+        <v>12</v>
+      </c>
+      <c r="K74" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>20</v>
+      </c>
+      <c r="B75" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
+      <c r="E75">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>26</v>
+      </c>
+      <c r="G75">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J75">
+        <v>13</v>
+      </c>
+      <c r="K75" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
+      <c r="E76">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F76">
+        <v>25</v>
+      </c>
+      <c r="G76">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="J76">
+        <v>14</v>
+      </c>
+      <c r="K76" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77">
+        <v>14</v>
+      </c>
+      <c r="E77">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G77">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="J77">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78">
+        <v>6</v>
+      </c>
+      <c r="D78">
+        <v>10</v>
+      </c>
+      <c r="E78">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="J78">
+        <v>16</v>
+      </c>
+      <c r="K78" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>8</v>
+      </c>
+      <c r="B79" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79">
+        <v>6</v>
+      </c>
+      <c r="D79">
+        <v>4</v>
+      </c>
+      <c r="E79">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="J79">
+        <v>17</v>
+      </c>
+      <c r="K79" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>137</v>
+      </c>
+      <c r="C80">
+        <v>6</v>
+      </c>
+      <c r="D80">
+        <v>2</v>
+      </c>
+      <c r="E80">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="J80">
+        <v>18</v>
+      </c>
+      <c r="K80" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J81">
+        <v>19</v>
+      </c>
+      <c r="K81" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>13</v>
+      </c>
+      <c r="B82" t="s">
+        <v>121</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82">
+        <v>4</v>
+      </c>
+      <c r="E82">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>20</v>
+      </c>
+      <c r="K82" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>21</v>
+      </c>
+      <c r="B83" t="s">
+        <v>129</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>5</v>
+      </c>
+      <c r="E83">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J83">
+        <v>21</v>
+      </c>
+      <c r="K83" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>22</v>
+      </c>
+      <c r="B84" t="s">
+        <v>130</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="J84">
+        <v>22</v>
+      </c>
+      <c r="K84" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>11</v>
+      </c>
+      <c r="B85" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J85">
+        <v>23</v>
+      </c>
+      <c r="K85" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>122</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J86">
+        <v>24</v>
+      </c>
+      <c r="K86" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>18</v>
+      </c>
+      <c r="B87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G87">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J87">
+        <v>25</v>
+      </c>
+      <c r="K87" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>24</v>
+      </c>
+      <c r="B88" t="s">
+        <v>132</v>
+      </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
+      <c r="E88">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G88">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J88">
+        <v>26</v>
+      </c>
+      <c r="K88" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>23</v>
+      </c>
+      <c r="B89" t="s">
+        <v>131</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>27</v>
+      </c>
+      <c r="B90" t="s">
+        <v>135</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>29</v>
+      </c>
+      <c r="B91" t="s">
+        <v>138</v>
+      </c>
+      <c r="E91">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J91" t="s">
+        <v>108</v>
+      </c>
+      <c r="K91" t="s">
+        <v>109</v>
+      </c>
+      <c r="L91" t="s">
+        <v>157</v>
+      </c>
+      <c r="M91" t="s">
+        <v>158</v>
+      </c>
+      <c r="N91" t="s">
+        <v>159</v>
+      </c>
+      <c r="O91" t="s">
+        <v>160</v>
+      </c>
+      <c r="P91" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>139</v>
+      </c>
+      <c r="E92">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>27</v>
+      </c>
+      <c r="K92" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>31</v>
+      </c>
+      <c r="B93" t="s">
+        <v>140</v>
+      </c>
+      <c r="E93">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>28</v>
+      </c>
+      <c r="K93" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>32</v>
+      </c>
+      <c r="B94" t="s">
+        <v>141</v>
+      </c>
+      <c r="E94">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>29</v>
+      </c>
+      <c r="K94" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>33</v>
+      </c>
+      <c r="B95" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>30</v>
+      </c>
+      <c r="K95" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>34</v>
+      </c>
+      <c r="B96" t="s">
+        <v>143</v>
+      </c>
+      <c r="E96">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>31</v>
+      </c>
+      <c r="K96" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>35</v>
+      </c>
+      <c r="B97" t="s">
+        <v>144</v>
+      </c>
+      <c r="E97">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>32</v>
+      </c>
+      <c r="K97" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>36</v>
+      </c>
+      <c r="B98" t="s">
+        <v>145</v>
+      </c>
+      <c r="E98">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>33</v>
+      </c>
+      <c r="K98" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>37</v>
+      </c>
+      <c r="B99" t="s">
+        <v>146</v>
+      </c>
+      <c r="E99">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>34</v>
+      </c>
+      <c r="K99" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>38</v>
+      </c>
+      <c r="B100" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>35</v>
+      </c>
+      <c r="K100" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>39</v>
+      </c>
+      <c r="B101" t="s">
+        <v>148</v>
+      </c>
+      <c r="E101">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>36</v>
+      </c>
+      <c r="K101" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>149</v>
+      </c>
+      <c r="E102">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>37</v>
+      </c>
+      <c r="K102" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>41</v>
+      </c>
+      <c r="B103" t="s">
+        <v>150</v>
+      </c>
+      <c r="E103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>38</v>
+      </c>
+      <c r="K103" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>151</v>
+      </c>
+      <c r="E104">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>39</v>
+      </c>
+      <c r="K104" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>43</v>
+      </c>
+      <c r="B105" t="s">
+        <v>152</v>
+      </c>
+      <c r="E105">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>40</v>
+      </c>
+      <c r="K105" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>44</v>
+      </c>
+      <c r="B106" t="s">
+        <v>153</v>
+      </c>
+      <c r="E106">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>41</v>
+      </c>
+      <c r="K106" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>45</v>
+      </c>
+      <c r="B107" t="s">
+        <v>154</v>
+      </c>
+      <c r="E107">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>42</v>
+      </c>
+      <c r="K107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>155</v>
+      </c>
+      <c r="E108">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>43</v>
+      </c>
+      <c r="K108" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>47</v>
+      </c>
+      <c r="B109" t="s">
+        <v>156</v>
+      </c>
+      <c r="E109">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>44</v>
+      </c>
+      <c r="K109" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E110">
+        <f t="shared" ref="E110:E112" si="2">C110+D110</f>
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <f t="shared" ref="G110:G112" si="3">E110+F110</f>
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>45</v>
+      </c>
+      <c r="K110" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E111">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>46</v>
+      </c>
+      <c r="K111" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E112">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>47</v>
+      </c>
+      <c r="K112" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
     <mergeCell ref="A49:A50"/>
     <mergeCell ref="A51:A52"/>
     <mergeCell ref="A2:D2"/>
@@ -2155,9 +3721,17 @@
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>